--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123163160</v>
+        <v>123166379</v>
       </c>
       <c r="B10" t="n">
-        <v>56078</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,39 +1527,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480236</v>
+        <v>480355</v>
       </c>
       <c r="R10" t="n">
-        <v>6790582</v>
+        <v>6790808</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123162937</v>
+        <v>123163160</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>56078</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,34 +1634,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480244</v>
+        <v>480236</v>
       </c>
       <c r="R11" t="n">
-        <v>6790562</v>
+        <v>6790582</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123164661</v>
+        <v>123162937</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480205</v>
+        <v>480244</v>
       </c>
       <c r="R12" t="n">
-        <v>6790666</v>
+        <v>6790562</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav I bakgrund.</t>
+          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123166379</v>
+        <v>123164661</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480355</v>
+        <v>480205</v>
       </c>
       <c r="R14" t="n">
-        <v>6790808</v>
+        <v>6790666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
+          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123162867</v>
+        <v>123161736</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480276</v>
+        <v>480289</v>
       </c>
       <c r="R2" t="n">
-        <v>6790526</v>
+        <v>6790544</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123161736</v>
+        <v>123159261</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480289</v>
+        <v>480416</v>
       </c>
       <c r="R3" t="n">
-        <v>6790544</v>
+        <v>6790569</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123164609</v>
+        <v>123160655</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480220</v>
+        <v>480315</v>
       </c>
       <c r="R4" t="n">
-        <v>6790638</v>
+        <v>6790533</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123164011</v>
+        <v>123164661</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480184</v>
+        <v>480205</v>
       </c>
       <c r="R5" t="n">
-        <v>6790641</v>
+        <v>6790666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
+          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123163199</v>
+        <v>123165979</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480198</v>
+        <v>480211</v>
       </c>
       <c r="R6" t="n">
-        <v>6790624</v>
+        <v>6790814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123160556</v>
+        <v>123163689</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480380</v>
+        <v>480184</v>
       </c>
       <c r="R7" t="n">
-        <v>6790556</v>
+        <v>6790641</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123159261</v>
+        <v>123164609</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480416</v>
+        <v>480220</v>
       </c>
       <c r="R8" t="n">
-        <v>6790569</v>
+        <v>6790638</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123160250</v>
+        <v>123159458</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1425,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480353</v>
+        <v>480398</v>
       </c>
       <c r="R9" t="n">
-        <v>6790515</v>
+        <v>6790566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123166379</v>
+        <v>123160404</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,34 +1532,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480355</v>
+        <v>480369</v>
       </c>
       <c r="R10" t="n">
-        <v>6790808</v>
+        <v>6790554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123163160</v>
+        <v>123164840</v>
       </c>
       <c r="B11" t="n">
-        <v>56078</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,39 +1639,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480236</v>
+        <v>480161</v>
       </c>
       <c r="R11" t="n">
-        <v>6790582</v>
+        <v>6790726</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123162937</v>
+        <v>123165065</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480244</v>
+        <v>480201</v>
       </c>
       <c r="R12" t="n">
-        <v>6790562</v>
+        <v>6790751</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Miljöbild och garnlav.</t>
+          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123164661</v>
+        <v>123160556</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1979,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480205</v>
+        <v>480380</v>
       </c>
       <c r="R14" t="n">
-        <v>6790666</v>
+        <v>6790556</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav I bakgrund.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123159458</v>
+        <v>123160250</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,39 +2067,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480398</v>
+        <v>480353</v>
       </c>
       <c r="R15" t="n">
-        <v>6790566</v>
+        <v>6790515</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123160404</v>
+        <v>123166379</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,39 +2169,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480369</v>
+        <v>480355</v>
       </c>
       <c r="R16" t="n">
-        <v>6790554</v>
+        <v>6790808</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,6 +2229,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123161260</v>
+        <v>123162867</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,34 +2276,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480315</v>
+        <v>480276</v>
       </c>
       <c r="R17" t="n">
-        <v>6790533</v>
+        <v>6790526</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123160655</v>
+        <v>123161260</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,29 +2485,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
@@ -2550,6 +2545,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123164840</v>
+        <v>123163160</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>56078</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,34 +2592,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480161</v>
+        <v>480236</v>
       </c>
       <c r="R20" t="n">
-        <v>6790726</v>
+        <v>6790582</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,11 +2657,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123165065</v>
+        <v>123162937</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480201</v>
+        <v>480244</v>
       </c>
       <c r="R21" t="n">
-        <v>6790751</v>
+        <v>6790562</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 50.</t>
+          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,7 +2790,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123165979</v>
+        <v>123163199</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480211</v>
+        <v>480198</v>
       </c>
       <c r="R22" t="n">
-        <v>6790814</v>
+        <v>6790624</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2868,11 +2868,6 @@
           <t>2025-03-13</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2894,6 +2889,113 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123162134</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>480299</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6790542</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav runt omkring kring mig.  Äldre skog med granar och tallar, många mer än 150 år.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123161736</v>
+        <v>123162937</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480289</v>
+        <v>480244</v>
       </c>
       <c r="R2" t="n">
-        <v>6790544</v>
+        <v>6790562</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123159261</v>
+        <v>123164661</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480416</v>
+        <v>480205</v>
       </c>
       <c r="R3" t="n">
-        <v>6790569</v>
+        <v>6790666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123160655</v>
+        <v>123162867</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -924,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480315</v>
+        <v>480276</v>
       </c>
       <c r="R4" t="n">
-        <v>6790533</v>
+        <v>6790526</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123164661</v>
+        <v>123159287</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480205</v>
+        <v>480431</v>
       </c>
       <c r="R5" t="n">
-        <v>6790666</v>
+        <v>6790550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123165979</v>
+        <v>123161260</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480211</v>
+        <v>480315</v>
       </c>
       <c r="R6" t="n">
-        <v>6790814</v>
+        <v>6790533</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
+          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123163689</v>
+        <v>123160404</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480184</v>
+        <v>480369</v>
       </c>
       <c r="R7" t="n">
-        <v>6790641</v>
+        <v>6790554</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123164609</v>
+        <v>123159261</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480220</v>
+        <v>480416</v>
       </c>
       <c r="R8" t="n">
-        <v>6790638</v>
+        <v>6790569</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123159458</v>
+        <v>123164840</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,39 +1430,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480398</v>
+        <v>480161</v>
       </c>
       <c r="R9" t="n">
-        <v>6790566</v>
+        <v>6790726</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123160404</v>
+        <v>123160250</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,39 +1537,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480369</v>
+        <v>480353</v>
       </c>
       <c r="R10" t="n">
-        <v>6790554</v>
+        <v>6790515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123164840</v>
+        <v>123166144</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,34 +1639,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480161</v>
+        <v>480211</v>
       </c>
       <c r="R11" t="n">
-        <v>6790726</v>
+        <v>6790814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123165065</v>
+        <v>123161736</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480201</v>
+        <v>480289</v>
       </c>
       <c r="R12" t="n">
-        <v>6790751</v>
+        <v>6790544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123166144</v>
+        <v>123159458</v>
       </c>
       <c r="B13" t="n">
         <v>57494</v>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480211</v>
+        <v>480398</v>
       </c>
       <c r="R13" t="n">
-        <v>6790814</v>
+        <v>6790566</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2051,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123160250</v>
+        <v>123164011</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2091,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480353</v>
+        <v>480184</v>
       </c>
       <c r="R15" t="n">
-        <v>6790515</v>
+        <v>6790641</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,6 +2122,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123166379</v>
+        <v>123164609</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480355</v>
+        <v>480220</v>
       </c>
       <c r="R16" t="n">
-        <v>6790808</v>
+        <v>6790638</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123162867</v>
+        <v>123163199</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,39 +2276,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480276</v>
+        <v>480198</v>
       </c>
       <c r="R17" t="n">
-        <v>6790526</v>
+        <v>6790624</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123159287</v>
+        <v>123165065</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2407,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480431</v>
+        <v>480201</v>
       </c>
       <c r="R18" t="n">
-        <v>6790550</v>
+        <v>6790751</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,6 +2438,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,7 +2469,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123161260</v>
+        <v>123166379</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480315</v>
+        <v>480355</v>
       </c>
       <c r="R19" t="n">
-        <v>6790533</v>
+        <v>6790808</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Garnlav i bakgrunden, miljöbild.</t>
+          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123163160</v>
+        <v>123160655</v>
       </c>
       <c r="B20" t="n">
-        <v>56078</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,27 +2592,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480236</v>
+        <v>480315</v>
       </c>
       <c r="R20" t="n">
-        <v>6790582</v>
+        <v>6790533</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123162937</v>
+        <v>123165979</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480244</v>
+        <v>480211</v>
       </c>
       <c r="R21" t="n">
-        <v>6790562</v>
+        <v>6790814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Miljöbild och garnlav.</t>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123163199</v>
+        <v>123163160</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>56078</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,34 +2806,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480198</v>
+        <v>480236</v>
       </c>
       <c r="R22" t="n">
-        <v>6790624</v>
+        <v>6790582</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123162937</v>
+        <v>123166144</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480244</v>
+        <v>480211</v>
       </c>
       <c r="R2" t="n">
-        <v>6790562</v>
+        <v>6790814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123164661</v>
+        <v>123160556</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480205</v>
+        <v>480380</v>
       </c>
       <c r="R3" t="n">
-        <v>6790666</v>
+        <v>6790556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav I bakgrund.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123162867</v>
+        <v>123164840</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480276</v>
+        <v>480161</v>
       </c>
       <c r="R4" t="n">
-        <v>6790526</v>
+        <v>6790726</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123159287</v>
+        <v>123164661</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480431</v>
+        <v>480205</v>
       </c>
       <c r="R5" t="n">
-        <v>6790550</v>
+        <v>6790666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123161260</v>
+        <v>123162937</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480315</v>
+        <v>480244</v>
       </c>
       <c r="R6" t="n">
-        <v>6790533</v>
+        <v>6790562</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Garnlav i bakgrunden, miljöbild.</t>
+          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123160404</v>
+        <v>123160655</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,16 +1226,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1241,7 +1246,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480369</v>
+        <v>480315</v>
       </c>
       <c r="R7" t="n">
-        <v>6790554</v>
+        <v>6790533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123159261</v>
+        <v>123160250</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480416</v>
+        <v>480353</v>
       </c>
       <c r="R8" t="n">
-        <v>6790569</v>
+        <v>6790515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123164840</v>
+        <v>123163199</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480161</v>
+        <v>480198</v>
       </c>
       <c r="R9" t="n">
-        <v>6790726</v>
+        <v>6790624</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123160250</v>
+        <v>123164011</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480353</v>
+        <v>480184</v>
       </c>
       <c r="R10" t="n">
-        <v>6790515</v>
+        <v>6790641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123166144</v>
+        <v>123166379</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,39 +1644,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480211</v>
+        <v>480355</v>
       </c>
       <c r="R11" t="n">
-        <v>6790814</v>
+        <v>6790808</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123161736</v>
+        <v>123163160</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>56078</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,34 +1751,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480289</v>
+        <v>480236</v>
       </c>
       <c r="R12" t="n">
-        <v>6790544</v>
+        <v>6790582</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123159458</v>
+        <v>123162703</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,39 +1858,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480398</v>
+        <v>480289</v>
       </c>
       <c r="R13" t="n">
-        <v>6790566</v>
+        <v>6790544</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1918,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder. Gammal skog i området, 150 år och mer, tall och gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123160556</v>
+        <v>123159598</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1979,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480380</v>
+        <v>480416</v>
       </c>
       <c r="R14" t="n">
-        <v>6790556</v>
+        <v>6790569</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Garnlav i bakgrund av kolad stubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123164011</v>
+        <v>123159458</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,34 +2072,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480184</v>
+        <v>480398</v>
       </c>
       <c r="R15" t="n">
-        <v>6790641</v>
+        <v>6790566</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123164609</v>
+        <v>123161260</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2193,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480220</v>
+        <v>480315</v>
       </c>
       <c r="R16" t="n">
-        <v>6790638</v>
+        <v>6790533</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
+          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123163199</v>
+        <v>123165979</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2300,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480198</v>
+        <v>480211</v>
       </c>
       <c r="R17" t="n">
-        <v>6790624</v>
+        <v>6790814</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,6 +2346,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123165065</v>
+        <v>123164609</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2402,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480201</v>
+        <v>480220</v>
       </c>
       <c r="R18" t="n">
-        <v>6790751</v>
+        <v>6790638</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 50.</t>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123166379</v>
+        <v>123159287</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2509,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480355</v>
+        <v>480431</v>
       </c>
       <c r="R19" t="n">
-        <v>6790808</v>
+        <v>6790550</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123160655</v>
+        <v>123165065</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,39 +2602,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480315</v>
+        <v>480201</v>
       </c>
       <c r="R20" t="n">
-        <v>6790533</v>
+        <v>6790751</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,6 +2662,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123165979</v>
+        <v>123162867</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,34 +2709,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480211</v>
+        <v>480276</v>
       </c>
       <c r="R21" t="n">
-        <v>6790814</v>
+        <v>6790526</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,11 +2774,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123163160</v>
+        <v>123160404</v>
       </c>
       <c r="B22" t="n">
-        <v>56078</v>
+        <v>57494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480236</v>
+        <v>480369</v>
       </c>
       <c r="R22" t="n">
-        <v>6790582</v>
+        <v>6790554</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123166144</v>
+        <v>123161260</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480211</v>
+        <v>480315</v>
       </c>
       <c r="R2" t="n">
-        <v>6790814</v>
+        <v>6790533</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123160556</v>
+        <v>123164661</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480380</v>
+        <v>480205</v>
       </c>
       <c r="R3" t="n">
-        <v>6790556</v>
+        <v>6790666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123164840</v>
+        <v>123160250</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480161</v>
+        <v>480353</v>
       </c>
       <c r="R4" t="n">
-        <v>6790726</v>
+        <v>6790515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123164661</v>
+        <v>123165065</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480205</v>
+        <v>480201</v>
       </c>
       <c r="R5" t="n">
-        <v>6790666</v>
+        <v>6790751</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav I bakgrund.</t>
+          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123162937</v>
+        <v>123163160</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>56081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480244</v>
+        <v>480236</v>
       </c>
       <c r="R6" t="n">
-        <v>6790562</v>
+        <v>6790582</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123160655</v>
+        <v>123159458</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,16 +1221,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480315</v>
+        <v>480398</v>
       </c>
       <c r="R7" t="n">
-        <v>6790533</v>
+        <v>6790566</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123160250</v>
+        <v>123166144</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,34 +1328,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480353</v>
+        <v>480211</v>
       </c>
       <c r="R8" t="n">
-        <v>6790515</v>
+        <v>6790814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123163199</v>
+        <v>123163689</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480198</v>
+        <v>480184</v>
       </c>
       <c r="R9" t="n">
-        <v>6790624</v>
+        <v>6790641</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123164011</v>
+        <v>123162703</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480184</v>
+        <v>480289</v>
       </c>
       <c r="R10" t="n">
-        <v>6790641</v>
+        <v>6790544</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
+          <t>Garnlav med miljöbilder. Gammal skog i området, 150 år och mer, tall och gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123166379</v>
+        <v>123159261</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480355</v>
+        <v>480416</v>
       </c>
       <c r="R11" t="n">
-        <v>6790808</v>
+        <v>6790569</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123163160</v>
+        <v>123164840</v>
       </c>
       <c r="B12" t="n">
-        <v>56078</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,39 +1746,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480236</v>
+        <v>480161</v>
       </c>
       <c r="R12" t="n">
-        <v>6790582</v>
+        <v>6790726</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,6 +1806,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123162703</v>
+        <v>123164609</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480289</v>
+        <v>480220</v>
       </c>
       <c r="R13" t="n">
-        <v>6790544</v>
+        <v>6790638</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbilder. Gammal skog i området, 150 år och mer, tall och gran.</t>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123159598</v>
+        <v>123160655</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,34 +1960,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480416</v>
+        <v>480315</v>
       </c>
       <c r="R14" t="n">
-        <v>6790569</v>
+        <v>6790533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,11 +2025,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrund av kolad stubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123159458</v>
+        <v>123163199</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,39 +2067,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480398</v>
+        <v>480198</v>
       </c>
       <c r="R15" t="n">
-        <v>6790566</v>
+        <v>6790624</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123161260</v>
+        <v>123160404</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,34 +2169,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480315</v>
+        <v>480369</v>
       </c>
       <c r="R16" t="n">
-        <v>6790533</v>
+        <v>6790554</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,11 +2234,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123165979</v>
+        <v>123166379</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480211</v>
+        <v>480355</v>
       </c>
       <c r="R17" t="n">
-        <v>6790814</v>
+        <v>6790808</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2340,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
+          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123164609</v>
+        <v>123162867</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,34 +2383,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480220</v>
+        <v>480276</v>
       </c>
       <c r="R18" t="n">
-        <v>6790638</v>
+        <v>6790526</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,11 +2448,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,7 +2477,7 @@
         <v>123159287</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123165065</v>
+        <v>123160556</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2626,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480201</v>
+        <v>480380</v>
       </c>
       <c r="R20" t="n">
-        <v>6790751</v>
+        <v>6790556</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2656,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 50.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123162867</v>
+        <v>123165979</v>
       </c>
       <c r="B21" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,39 +2699,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480276</v>
+        <v>480211</v>
       </c>
       <c r="R21" t="n">
-        <v>6790526</v>
+        <v>6790814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,6 +2759,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123160404</v>
+        <v>123162937</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,39 +2806,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480369</v>
+        <v>480244</v>
       </c>
       <c r="R22" t="n">
-        <v>6790554</v>
+        <v>6790562</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,6 +2866,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,7 +2900,7 @@
         <v>123162134</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123161260</v>
+        <v>123163689</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480315</v>
+        <v>480184</v>
       </c>
       <c r="R2" t="n">
-        <v>6790533</v>
+        <v>6790641</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123164661</v>
+        <v>123165065</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480205</v>
+        <v>480201</v>
       </c>
       <c r="R3" t="n">
-        <v>6790666</v>
+        <v>6790751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav I bakgrund.</t>
+          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123160250</v>
+        <v>123160404</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480353</v>
+        <v>480369</v>
       </c>
       <c r="R4" t="n">
-        <v>6790515</v>
+        <v>6790554</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123165065</v>
+        <v>123159261</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480201</v>
+        <v>480416</v>
       </c>
       <c r="R5" t="n">
-        <v>6790751</v>
+        <v>6790569</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123163160</v>
+        <v>123165979</v>
       </c>
       <c r="B6" t="n">
-        <v>56081</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480236</v>
+        <v>480211</v>
       </c>
       <c r="R6" t="n">
-        <v>6790582</v>
+        <v>6790814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123159458</v>
+        <v>123161260</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,39 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480398</v>
+        <v>480315</v>
       </c>
       <c r="R7" t="n">
-        <v>6790566</v>
+        <v>6790533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123166144</v>
+        <v>123161736</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,39 +1323,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480211</v>
+        <v>480289</v>
       </c>
       <c r="R8" t="n">
-        <v>6790814</v>
+        <v>6790544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123163689</v>
+        <v>123162937</v>
       </c>
       <c r="B9" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480184</v>
+        <v>480244</v>
       </c>
       <c r="R9" t="n">
-        <v>6790641</v>
+        <v>6790562</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123162703</v>
+        <v>123166379</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480289</v>
+        <v>480355</v>
       </c>
       <c r="R10" t="n">
-        <v>6790544</v>
+        <v>6790808</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbilder. Gammal skog i området, 150 år och mer, tall och gran.</t>
+          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123159261</v>
+        <v>123163199</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480416</v>
+        <v>480198</v>
       </c>
       <c r="R11" t="n">
-        <v>6790569</v>
+        <v>6790624</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123164840</v>
+        <v>123159458</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>57497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,34 +1741,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480161</v>
+        <v>480398</v>
       </c>
       <c r="R12" t="n">
-        <v>6790726</v>
+        <v>6790566</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123164609</v>
+        <v>123159287</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480220</v>
+        <v>480431</v>
       </c>
       <c r="R13" t="n">
-        <v>6790638</v>
+        <v>6790550</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123160655</v>
+        <v>123166144</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,16 +1950,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1989,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480315</v>
+        <v>480211</v>
       </c>
       <c r="R14" t="n">
-        <v>6790533</v>
+        <v>6790814</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123163199</v>
+        <v>123164840</v>
       </c>
       <c r="B15" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480198</v>
+        <v>480161</v>
       </c>
       <c r="R15" t="n">
-        <v>6790624</v>
+        <v>6790726</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,6 +2117,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123160404</v>
+        <v>123160556</v>
       </c>
       <c r="B16" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,39 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480369</v>
+        <v>480380</v>
       </c>
       <c r="R16" t="n">
-        <v>6790554</v>
+        <v>6790556</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,6 +2224,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123166379</v>
+        <v>123160655</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,34 +2271,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480355</v>
+        <v>480315</v>
       </c>
       <c r="R17" t="n">
-        <v>6790808</v>
+        <v>6790533</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,11 +2336,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123162867</v>
+        <v>123164609</v>
       </c>
       <c r="B18" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,39 +2378,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480276</v>
+        <v>480220</v>
       </c>
       <c r="R18" t="n">
-        <v>6790526</v>
+        <v>6790638</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,6 +2438,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123159287</v>
+        <v>123162867</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>57497</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,34 +2485,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480431</v>
+        <v>480276</v>
       </c>
       <c r="R19" t="n">
-        <v>6790550</v>
+        <v>6790526</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123160556</v>
+        <v>123160250</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480380</v>
+        <v>480353</v>
       </c>
       <c r="R20" t="n">
-        <v>6790556</v>
+        <v>6790515</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,11 +2652,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123165979</v>
+        <v>123164661</v>
       </c>
       <c r="B21" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480211</v>
+        <v>480205</v>
       </c>
       <c r="R21" t="n">
-        <v>6790814</v>
+        <v>6790666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2758,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
+          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123162937</v>
+        <v>123163160</v>
       </c>
       <c r="B22" t="n">
-        <v>78769</v>
+        <v>56081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,34 +2801,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480244</v>
+        <v>480236</v>
       </c>
       <c r="R22" t="n">
-        <v>6790562</v>
+        <v>6790582</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,11 +2866,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2900,7 +2895,7 @@
         <v>123162134</v>
       </c>
       <c r="B23" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123163689</v>
+        <v>123162937</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480184</v>
+        <v>480244</v>
       </c>
       <c r="R2" t="n">
-        <v>6790641</v>
+        <v>6790562</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123165065</v>
+        <v>123164840</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480201</v>
+        <v>480161</v>
       </c>
       <c r="R3" t="n">
-        <v>6790751</v>
+        <v>6790726</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 50.</t>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123160404</v>
+        <v>123165979</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480369</v>
+        <v>480211</v>
       </c>
       <c r="R4" t="n">
-        <v>6790554</v>
+        <v>6790814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123159261</v>
+        <v>123161736</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480416</v>
+        <v>480289</v>
       </c>
       <c r="R5" t="n">
-        <v>6790569</v>
+        <v>6790544</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123165979</v>
+        <v>123160655</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480211</v>
+        <v>480315</v>
       </c>
       <c r="R6" t="n">
-        <v>6790814</v>
+        <v>6790533</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123161260</v>
+        <v>123162867</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480315</v>
+        <v>480276</v>
       </c>
       <c r="R7" t="n">
-        <v>6790533</v>
+        <v>6790526</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123161736</v>
+        <v>123159261</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480289</v>
+        <v>480416</v>
       </c>
       <c r="R8" t="n">
-        <v>6790544</v>
+        <v>6790569</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123162937</v>
+        <v>123161260</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480244</v>
+        <v>480315</v>
       </c>
       <c r="R9" t="n">
-        <v>6790562</v>
+        <v>6790533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Miljöbild och garnlav.</t>
+          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123166379</v>
+        <v>123163160</v>
       </c>
       <c r="B10" t="n">
-        <v>78771</v>
+        <v>56081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,34 +1537,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480355</v>
+        <v>480236</v>
       </c>
       <c r="R10" t="n">
-        <v>6790808</v>
+        <v>6790582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123163199</v>
+        <v>123160250</v>
       </c>
       <c r="B11" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480198</v>
+        <v>480353</v>
       </c>
       <c r="R11" t="n">
-        <v>6790624</v>
+        <v>6790515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123159458</v>
+        <v>123165065</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>78772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,39 +1746,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480398</v>
+        <v>480201</v>
       </c>
       <c r="R12" t="n">
-        <v>6790566</v>
+        <v>6790751</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1806,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123159287</v>
+        <v>123163689</v>
       </c>
       <c r="B13" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480431</v>
+        <v>480184</v>
       </c>
       <c r="R13" t="n">
-        <v>6790550</v>
+        <v>6790641</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123166144</v>
+        <v>123164661</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,39 +1955,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480211</v>
+        <v>480205</v>
       </c>
       <c r="R14" t="n">
-        <v>6790814</v>
+        <v>6790666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,6 +2015,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123164840</v>
+        <v>123163199</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480161</v>
+        <v>480198</v>
       </c>
       <c r="R15" t="n">
-        <v>6790726</v>
+        <v>6790624</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,11 +2122,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123160556</v>
+        <v>123160404</v>
       </c>
       <c r="B16" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,34 +2164,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480380</v>
+        <v>480369</v>
       </c>
       <c r="R16" t="n">
-        <v>6790556</v>
+        <v>6790554</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,11 +2229,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123160655</v>
+        <v>123159287</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,39 +2271,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480315</v>
+        <v>480431</v>
       </c>
       <c r="R17" t="n">
-        <v>6790533</v>
+        <v>6790550</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123164609</v>
+        <v>123166144</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2378,34 +2373,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480220</v>
+        <v>480211</v>
       </c>
       <c r="R18" t="n">
-        <v>6790638</v>
+        <v>6790814</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,11 +2438,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123162867</v>
+        <v>123160556</v>
       </c>
       <c r="B19" t="n">
-        <v>57497</v>
+        <v>78772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,39 +2480,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480276</v>
+        <v>480380</v>
       </c>
       <c r="R19" t="n">
-        <v>6790526</v>
+        <v>6790556</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,6 +2540,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123160250</v>
+        <v>123164609</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480353</v>
+        <v>480220</v>
       </c>
       <c r="R20" t="n">
-        <v>6790515</v>
+        <v>6790638</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,6 +2647,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123164661</v>
+        <v>123159458</v>
       </c>
       <c r="B21" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,34 +2694,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480205</v>
+        <v>480398</v>
       </c>
       <c r="R21" t="n">
-        <v>6790666</v>
+        <v>6790566</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,11 +2759,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123163160</v>
+        <v>123166379</v>
       </c>
       <c r="B22" t="n">
-        <v>56081</v>
+        <v>78772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,39 +2801,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480236</v>
+        <v>480355</v>
       </c>
       <c r="R22" t="n">
-        <v>6790582</v>
+        <v>6790808</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,6 +2861,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2895,7 +2895,7 @@
         <v>123162134</v>
       </c>
       <c r="B23" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123166144</v>
+        <v>123162703</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>78775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,39 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480211</v>
+        <v>480289</v>
       </c>
       <c r="R10" t="n">
-        <v>6790814</v>
+        <v>6790544</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder. Gammal skog i området, 150 år och mer, tall och gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123162703</v>
+        <v>123166144</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,34 +1639,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480289</v>
+        <v>480211</v>
       </c>
       <c r="R11" t="n">
-        <v>6790544</v>
+        <v>6790814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder. Gammal skog i området, 150 år och mer, tall och gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123163689</v>
+        <v>123164011</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123165065</v>
+        <v>123164661</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480201</v>
+        <v>480205</v>
       </c>
       <c r="R3" t="n">
-        <v>6790751</v>
+        <v>6790666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 50.</t>
+          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123159287</v>
+        <v>123163199</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480431</v>
+        <v>480198</v>
       </c>
       <c r="R4" t="n">
-        <v>6790550</v>
+        <v>6790624</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123162867</v>
+        <v>123165979</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480276</v>
+        <v>480211</v>
       </c>
       <c r="R5" t="n">
-        <v>6790526</v>
+        <v>6790814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123159598</v>
+        <v>123162867</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>57503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480416</v>
+        <v>480276</v>
       </c>
       <c r="R6" t="n">
-        <v>6790569</v>
+        <v>6790526</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrund av kolad stubbe.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123164840</v>
+        <v>123159598</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480161</v>
+        <v>480416</v>
       </c>
       <c r="R7" t="n">
-        <v>6790726</v>
+        <v>6790569</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
+          <t>Garnlav i bakgrund av kolad stubbe.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123166379</v>
+        <v>123162937</v>
       </c>
       <c r="B8" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480355</v>
+        <v>480244</v>
       </c>
       <c r="R8" t="n">
-        <v>6790808</v>
+        <v>6790562</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
+          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123160250</v>
+        <v>123159287</v>
       </c>
       <c r="B9" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480353</v>
+        <v>480431</v>
       </c>
       <c r="R9" t="n">
-        <v>6790515</v>
+        <v>6790550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123162703</v>
+        <v>123164609</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480289</v>
+        <v>480220</v>
       </c>
       <c r="R10" t="n">
-        <v>6790544</v>
+        <v>6790638</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbilder. Gammal skog i området, 150 år och mer, tall och gran.</t>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123166144</v>
+        <v>123161260</v>
       </c>
       <c r="B11" t="n">
-        <v>57497</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,39 +1644,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480211</v>
+        <v>480315</v>
       </c>
       <c r="R11" t="n">
-        <v>6790814</v>
+        <v>6790533</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123161260</v>
+        <v>123160404</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>57503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,34 +1751,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480315</v>
+        <v>480369</v>
       </c>
       <c r="R12" t="n">
-        <v>6790533</v>
+        <v>6790554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123164609</v>
+        <v>123162703</v>
       </c>
       <c r="B13" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480220</v>
+        <v>480289</v>
       </c>
       <c r="R13" t="n">
-        <v>6790638</v>
+        <v>6790544</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
+          <t>Garnlav med miljöbilder. Gammal skog i området, 150 år och mer, tall och gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123165979</v>
+        <v>123163160</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>56087</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,34 +1965,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480211</v>
+        <v>480236</v>
       </c>
       <c r="R14" t="n">
-        <v>6790814</v>
+        <v>6790582</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123163199</v>
+        <v>123165065</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480198</v>
+        <v>480201</v>
       </c>
       <c r="R15" t="n">
-        <v>6790624</v>
+        <v>6790751</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,6 +2132,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123163160</v>
+        <v>123160655</v>
       </c>
       <c r="B16" t="n">
-        <v>56081</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,27 +2179,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2198,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480236</v>
+        <v>480315</v>
       </c>
       <c r="R16" t="n">
-        <v>6790582</v>
+        <v>6790533</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123162937</v>
+        <v>123164840</v>
       </c>
       <c r="B17" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2300,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480244</v>
+        <v>480161</v>
       </c>
       <c r="R17" t="n">
-        <v>6790562</v>
+        <v>6790726</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Miljöbild och garnlav.</t>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123160655</v>
+        <v>123160556</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,39 +2393,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480315</v>
+        <v>480380</v>
       </c>
       <c r="R18" t="n">
-        <v>6790533</v>
+        <v>6790556</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,6 +2453,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123160556</v>
+        <v>123160250</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480380</v>
+        <v>480353</v>
       </c>
       <c r="R19" t="n">
-        <v>6790556</v>
+        <v>6790515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123160404</v>
+        <v>123159458</v>
       </c>
       <c r="B20" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,7 +2622,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2626,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480369</v>
+        <v>480398</v>
       </c>
       <c r="R20" t="n">
-        <v>6790554</v>
+        <v>6790566</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123164661</v>
+        <v>123166379</v>
       </c>
       <c r="B21" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2728,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480205</v>
+        <v>480355</v>
       </c>
       <c r="R21" t="n">
-        <v>6790666</v>
+        <v>6790808</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav I bakgrund.</t>
+          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123159458</v>
+        <v>123166144</v>
       </c>
       <c r="B22" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480398</v>
+        <v>480211</v>
       </c>
       <c r="R22" t="n">
-        <v>6790566</v>
+        <v>6790814</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2910,7 @@
         <v>123162134</v>
       </c>
       <c r="B23" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123160655</v>
+        <v>123164840</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,39 +2179,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480315</v>
+        <v>480161</v>
       </c>
       <c r="R16" t="n">
-        <v>6790533</v>
+        <v>6790726</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,6 +2239,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123164840</v>
+        <v>123160655</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,34 +2286,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480161</v>
+        <v>480315</v>
       </c>
       <c r="R17" t="n">
-        <v>6790726</v>
+        <v>6790533</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,11 +2351,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123164840</v>
+        <v>123160655</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,34 +2179,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480161</v>
+        <v>480315</v>
       </c>
       <c r="R16" t="n">
-        <v>6790726</v>
+        <v>6790533</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,11 +2244,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123160655</v>
+        <v>123164840</v>
       </c>
       <c r="B17" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,39 +2286,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480315</v>
+        <v>480161</v>
       </c>
       <c r="R17" t="n">
-        <v>6790533</v>
+        <v>6790726</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2346,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123164011</v>
+        <v>123164840</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480184</v>
+        <v>480161</v>
       </c>
       <c r="R2" t="n">
-        <v>6790641</v>
+        <v>6790726</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123164661</v>
+        <v>123160655</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480205</v>
+        <v>480315</v>
       </c>
       <c r="R3" t="n">
-        <v>6790666</v>
+        <v>6790533</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123163199</v>
+        <v>123164609</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480198</v>
+        <v>480220</v>
       </c>
       <c r="R4" t="n">
-        <v>6790624</v>
+        <v>6790638</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123165979</v>
+        <v>123166379</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480211</v>
+        <v>480355</v>
       </c>
       <c r="R5" t="n">
-        <v>6790814</v>
+        <v>6790808</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
+          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123162867</v>
+        <v>123159261</v>
       </c>
       <c r="B6" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480276</v>
+        <v>480416</v>
       </c>
       <c r="R6" t="n">
-        <v>6790526</v>
+        <v>6790569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123159598</v>
+        <v>123163160</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>56090</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480416</v>
+        <v>480236</v>
       </c>
       <c r="R7" t="n">
-        <v>6790569</v>
+        <v>6790582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrund av kolad stubbe.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123162937</v>
+        <v>123164661</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480244</v>
+        <v>480205</v>
       </c>
       <c r="R8" t="n">
-        <v>6790562</v>
+        <v>6790666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Miljöbild och garnlav.</t>
+          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123159287</v>
+        <v>123161260</v>
       </c>
       <c r="B9" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480431</v>
+        <v>480315</v>
       </c>
       <c r="R9" t="n">
-        <v>6790550</v>
+        <v>6790533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123164609</v>
+        <v>123162867</v>
       </c>
       <c r="B10" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,34 +1542,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480220</v>
+        <v>480276</v>
       </c>
       <c r="R10" t="n">
-        <v>6790638</v>
+        <v>6790526</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1607,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123161260</v>
+        <v>123162937</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480315</v>
+        <v>480244</v>
       </c>
       <c r="R11" t="n">
-        <v>6790533</v>
+        <v>6790562</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Garnlav i bakgrunden, miljöbild.</t>
+          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123160404</v>
+        <v>123165065</v>
       </c>
       <c r="B12" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,39 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480369</v>
+        <v>480201</v>
       </c>
       <c r="R12" t="n">
-        <v>6790554</v>
+        <v>6790751</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123162703</v>
+        <v>123166144</v>
       </c>
       <c r="B13" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,34 +1863,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480289</v>
+        <v>480211</v>
       </c>
       <c r="R13" t="n">
-        <v>6790544</v>
+        <v>6790814</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1928,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder. Gammal skog i området, 150 år och mer, tall och gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123163160</v>
+        <v>123160250</v>
       </c>
       <c r="B14" t="n">
-        <v>56087</v>
+        <v>78786</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,39 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480236</v>
+        <v>480353</v>
       </c>
       <c r="R14" t="n">
-        <v>6790582</v>
+        <v>6790515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123165065</v>
+        <v>123160556</v>
       </c>
       <c r="B15" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480201</v>
+        <v>480380</v>
       </c>
       <c r="R15" t="n">
-        <v>6790751</v>
+        <v>6790556</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 50.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123164840</v>
+        <v>123163199</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480161</v>
+        <v>480198</v>
       </c>
       <c r="R16" t="n">
-        <v>6790726</v>
+        <v>6790624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123160655</v>
+        <v>123161736</v>
       </c>
       <c r="B17" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,39 +2281,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480315</v>
+        <v>480289</v>
       </c>
       <c r="R17" t="n">
-        <v>6790533</v>
+        <v>6790544</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123160556</v>
+        <v>123160404</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,34 +2383,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480380</v>
+        <v>480369</v>
       </c>
       <c r="R18" t="n">
-        <v>6790556</v>
+        <v>6790554</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,11 +2448,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123160250</v>
+        <v>123159458</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,34 +2490,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480353</v>
+        <v>480398</v>
       </c>
       <c r="R19" t="n">
-        <v>6790515</v>
+        <v>6790566</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123159458</v>
+        <v>123159287</v>
       </c>
       <c r="B20" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,39 +2597,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480398</v>
+        <v>480431</v>
       </c>
       <c r="R20" t="n">
-        <v>6790566</v>
+        <v>6790550</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123166379</v>
+        <v>123163689</v>
       </c>
       <c r="B21" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480355</v>
+        <v>480184</v>
       </c>
       <c r="R21" t="n">
-        <v>6790808</v>
+        <v>6790641</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,11 +2759,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123166144</v>
+        <v>123165979</v>
       </c>
       <c r="B22" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,29 +2801,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
@@ -2881,6 +2861,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,7 +2895,7 @@
         <v>123162134</v>
       </c>
       <c r="B23" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123164840</v>
+        <v>123161260</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480161</v>
+        <v>480315</v>
       </c>
       <c r="R2" t="n">
-        <v>6790726</v>
+        <v>6790533</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
+          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123160655</v>
+        <v>123159598</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480315</v>
+        <v>480416</v>
       </c>
       <c r="R3" t="n">
-        <v>6790533</v>
+        <v>6790569</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Garnlav i bakgrund av kolad stubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123164609</v>
+        <v>123164840</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480220</v>
+        <v>480161</v>
       </c>
       <c r="R4" t="n">
-        <v>6790638</v>
+        <v>6790726</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123166379</v>
+        <v>123164661</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480355</v>
+        <v>480205</v>
       </c>
       <c r="R5" t="n">
-        <v>6790808</v>
+        <v>6790666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
+          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123159261</v>
+        <v>123161736</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480416</v>
+        <v>480289</v>
       </c>
       <c r="R6" t="n">
-        <v>6790569</v>
+        <v>6790544</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123164661</v>
+        <v>123159287</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480205</v>
+        <v>480431</v>
       </c>
       <c r="R8" t="n">
-        <v>6790666</v>
+        <v>6790550</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123161260</v>
+        <v>123160250</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480315</v>
+        <v>480353</v>
       </c>
       <c r="R9" t="n">
-        <v>6790533</v>
+        <v>6790515</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123162867</v>
+        <v>123165065</v>
       </c>
       <c r="B10" t="n">
-        <v>57506</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,39 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480276</v>
+        <v>480201</v>
       </c>
       <c r="R10" t="n">
-        <v>6790526</v>
+        <v>6790751</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123162937</v>
+        <v>123165979</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480244</v>
+        <v>480211</v>
       </c>
       <c r="R11" t="n">
-        <v>6790562</v>
+        <v>6790814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Miljöbild och garnlav.</t>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123165065</v>
+        <v>123159458</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,34 +1746,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480201</v>
+        <v>480398</v>
       </c>
       <c r="R12" t="n">
-        <v>6790751</v>
+        <v>6790566</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123166144</v>
+        <v>123160556</v>
       </c>
       <c r="B13" t="n">
-        <v>57506</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,39 +1853,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480211</v>
+        <v>480380</v>
       </c>
       <c r="R13" t="n">
-        <v>6790814</v>
+        <v>6790556</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,6 +1913,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123160250</v>
+        <v>123162937</v>
       </c>
       <c r="B14" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480353</v>
+        <v>480244</v>
       </c>
       <c r="R14" t="n">
-        <v>6790515</v>
+        <v>6790562</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123160556</v>
+        <v>123163689</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480380</v>
+        <v>480184</v>
       </c>
       <c r="R15" t="n">
-        <v>6790556</v>
+        <v>6790641</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2127,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123163199</v>
+        <v>123164609</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480198</v>
+        <v>480220</v>
       </c>
       <c r="R16" t="n">
-        <v>6790624</v>
+        <v>6790638</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,6 +2229,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123161736</v>
+        <v>123162867</v>
       </c>
       <c r="B17" t="n">
-        <v>78786</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,34 +2276,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480289</v>
+        <v>480276</v>
       </c>
       <c r="R17" t="n">
-        <v>6790544</v>
+        <v>6790526</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123160404</v>
+        <v>123160655</v>
       </c>
       <c r="B18" t="n">
-        <v>57506</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,16 +2383,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2403,7 +2403,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480369</v>
+        <v>480315</v>
       </c>
       <c r="R18" t="n">
-        <v>6790554</v>
+        <v>6790533</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123159458</v>
+        <v>123160404</v>
       </c>
       <c r="B19" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480398</v>
+        <v>480369</v>
       </c>
       <c r="R19" t="n">
-        <v>6790566</v>
+        <v>6790554</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123159287</v>
+        <v>123166144</v>
       </c>
       <c r="B20" t="n">
-        <v>78786</v>
+        <v>57507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,34 +2597,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480431</v>
+        <v>480211</v>
       </c>
       <c r="R20" t="n">
-        <v>6790550</v>
+        <v>6790814</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123163689</v>
+        <v>123163199</v>
       </c>
       <c r="B21" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480184</v>
+        <v>480198</v>
       </c>
       <c r="R21" t="n">
-        <v>6790641</v>
+        <v>6790624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123165979</v>
+        <v>123166379</v>
       </c>
       <c r="B22" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2825,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480211</v>
+        <v>480355</v>
       </c>
       <c r="R22" t="n">
-        <v>6790814</v>
+        <v>6790808</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2870,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
+          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2895,7 +2900,7 @@
         <v>123162134</v>
       </c>
       <c r="B23" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123160250</v>
+        <v>123159458</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,34 +1430,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480353</v>
+        <v>480398</v>
       </c>
       <c r="R9" t="n">
-        <v>6790515</v>
+        <v>6790566</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123165065</v>
+        <v>123160250</v>
       </c>
       <c r="B10" t="n">
         <v>78788</v>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480201</v>
+        <v>480353</v>
       </c>
       <c r="R10" t="n">
-        <v>6790751</v>
+        <v>6790515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123165979</v>
+        <v>123165065</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480211</v>
+        <v>480201</v>
       </c>
       <c r="R11" t="n">
-        <v>6790814</v>
+        <v>6790751</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
+          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123159458</v>
+        <v>123165979</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,39 +1746,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480398</v>
+        <v>480211</v>
       </c>
       <c r="R12" t="n">
-        <v>6790566</v>
+        <v>6790814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1806,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123161260</v>
+        <v>123159161</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480315</v>
+        <v>480475</v>
       </c>
       <c r="R2" t="n">
-        <v>6790533</v>
+        <v>6790607</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123159598</v>
+        <v>123159261</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -858,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrund av kolad stubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123164840</v>
+        <v>123159287</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480161</v>
+        <v>480431</v>
       </c>
       <c r="R4" t="n">
-        <v>6790726</v>
+        <v>6790550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123164661</v>
+        <v>123160250</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480205</v>
+        <v>480353</v>
       </c>
       <c r="R5" t="n">
-        <v>6790666</v>
+        <v>6790515</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123161736</v>
+        <v>123160556</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480289</v>
+        <v>480380</v>
       </c>
       <c r="R6" t="n">
-        <v>6790544</v>
+        <v>6790556</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,55 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123163160</v>
+        <v>123161260</v>
       </c>
       <c r="B7" t="n">
-        <v>56090</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480236</v>
+        <v>480315</v>
       </c>
       <c r="R7" t="n">
-        <v>6790582</v>
+        <v>6790533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Garnlav i bakgrunden, miljöbild.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,19 +1267,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123159287</v>
+        <v>123161736</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1352,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480431</v>
+        <v>480289</v>
       </c>
       <c r="R8" t="n">
-        <v>6790550</v>
+        <v>6790544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,55 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123159458</v>
+        <v>123162134</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480398</v>
+        <v>480299</v>
       </c>
       <c r="R9" t="n">
-        <v>6790566</v>
+        <v>6790542</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav runt omkring kring mig.  Äldre skog med granar och tallar, många mer än 150 år.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,19 +1466,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123160250</v>
+        <v>123162937</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1561,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480353</v>
+        <v>480244</v>
       </c>
       <c r="R10" t="n">
-        <v>6790515</v>
+        <v>6790562</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1537,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild och garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,19 +1568,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123165065</v>
+        <v>123163030</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1663,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480201</v>
+        <v>480219</v>
       </c>
       <c r="R11" t="n">
-        <v>6790751</v>
+        <v>6790591</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1639,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,19 +1665,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123165979</v>
+        <v>123163199</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1770,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480211</v>
+        <v>480198</v>
       </c>
       <c r="R12" t="n">
-        <v>6790814</v>
+        <v>6790624</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,19 +1762,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123160556</v>
+        <v>123163689</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1877,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480380</v>
+        <v>480184</v>
       </c>
       <c r="R13" t="n">
-        <v>6790556</v>
+        <v>6790641</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1833,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,19 +1859,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123162937</v>
+        <v>123164609</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1984,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480244</v>
+        <v>480220</v>
       </c>
       <c r="R14" t="n">
-        <v>6790562</v>
+        <v>6790638</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,7 +1934,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbild och garnlav.</t>
+          <t>Miljöbild med garnlav i bakgrund.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,19 +1961,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123163689</v>
+        <v>123164661</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2091,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480184</v>
+        <v>480205</v>
       </c>
       <c r="R15" t="n">
-        <v>6790641</v>
+        <v>6790666</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,6 +2032,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav I bakgrund.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,19 +2063,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123164609</v>
+        <v>123164840</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2193,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480220</v>
+        <v>480161</v>
       </c>
       <c r="R16" t="n">
-        <v>6790638</v>
+        <v>6790726</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2138,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbild med garnlav i bakgrund.</t>
+          <t>Miljöbilder med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,55 +2165,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123162867</v>
+        <v>123165065</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480276</v>
+        <v>480201</v>
       </c>
       <c r="R17" t="n">
-        <v>6790526</v>
+        <v>6790751</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,6 +2236,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 50.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,55 +2267,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123160655</v>
+        <v>123165979</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480315</v>
+        <v>480211</v>
       </c>
       <c r="R18" t="n">
-        <v>6790533</v>
+        <v>6790814</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,6 +2338,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,55 +2369,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123160404</v>
+        <v>123166264</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480369</v>
+        <v>480341</v>
       </c>
       <c r="R19" t="n">
-        <v>6790554</v>
+        <v>6790831</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,6 +2440,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i en radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,55 +2471,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123166144</v>
+        <v>123166379</v>
       </c>
       <c r="B20" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480211</v>
+        <v>480355</v>
       </c>
       <c r="R20" t="n">
-        <v>6790814</v>
+        <v>6790808</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,6 +2542,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,50 +2573,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123163199</v>
+        <v>123159458</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480198</v>
+        <v>480398</v>
       </c>
       <c r="R21" t="n">
-        <v>6790624</v>
+        <v>6790566</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2790,50 +2675,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123166379</v>
+        <v>123160404</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480355</v>
+        <v>480369</v>
       </c>
       <c r="R22" t="n">
-        <v>6790808</v>
+        <v>6790554</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,11 +2751,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav i radie av ca 30 meter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,50 +2777,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123162134</v>
+        <v>123162867</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480299</v>
+        <v>480276</v>
       </c>
       <c r="R23" t="n">
-        <v>6790542</v>
+        <v>6790526</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,11 +2853,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Miljöbild med garnlav runt omkring kring mig.  Äldre skog med granar och tallar, många mer än 150 år.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,41 +2879,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132628463</v>
+        <v>123166144</v>
       </c>
       <c r="B24" t="n">
-        <v>91938</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480387</v>
+        <v>480211</v>
       </c>
       <c r="R24" t="n">
-        <v>6790513</v>
+        <v>6790814</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3065,22 +2949,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3095,57 +2969,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Christer Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Christer Lindberg</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132628770</v>
+        <v>123160655</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480387</v>
+        <v>480315</v>
       </c>
       <c r="R25" t="n">
-        <v>6790513</v>
+        <v>6790533</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3172,27 +3051,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>90 plantor</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3207,15 +3071,433 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123160720</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>480293</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6790512</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123163160</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>480236</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6790582</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132628770</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>480387</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6790513</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>90 plantor</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Christer Lindberg</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Christer Lindberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123158872</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hedsvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>480502</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6790591</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i omgivningen.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AZ117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945038</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945050</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945068</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945073</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945077</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945083</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945085</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945010</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945011</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945016</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945020</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944975</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945018</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945022</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945030</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945054</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945081</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945031</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945017</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945021</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945032</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945037</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945064</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945072</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945001</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3770,6 +3915,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123158872</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3867,6 +4017,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123159161</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3964,6 +4119,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123159261</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4061,6 +4221,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123159287</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4158,6 +4323,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123160250</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4260,6 +4430,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123160556</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4362,6 +4537,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123161260</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4459,6 +4639,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123161736</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4561,6 +4746,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123162134</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4663,6 +4853,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123162937</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4760,6 +4955,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123163030</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4857,6 +5057,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123163199</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4954,6 +5159,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123163689</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5056,6 +5266,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123164609</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5158,6 +5373,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123164661</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5260,6 +5480,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123164840</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5362,6 +5587,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123165065</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5464,6 +5694,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123165979</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5566,6 +5801,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123166264</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5668,6 +5908,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123166379</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5775,6 +6020,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945005</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5882,6 +6132,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945006</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5989,6 +6244,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945008</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6096,6 +6356,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945019</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6203,6 +6468,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945026</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6310,6 +6580,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945027</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6417,6 +6692,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945028</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6524,6 +6804,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945029</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6631,6 +6916,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945034</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6738,6 +7028,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945035</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6845,6 +7140,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945036</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6952,6 +7252,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945043</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7059,6 +7364,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945045</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7166,6 +7476,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945048</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7273,6 +7588,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945049</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7380,6 +7700,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945051</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7487,6 +7812,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945052</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7594,6 +7924,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945055</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7701,6 +8036,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945057</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7808,6 +8148,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945058</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7915,6 +8260,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945059</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8022,6 +8372,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945062</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8129,6 +8484,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945066</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8236,6 +8596,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945067</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8343,6 +8708,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945069</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8450,6 +8820,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945070</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8557,6 +8932,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945074</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8664,6 +9044,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945075</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8771,6 +9156,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945076</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8878,6 +9268,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945079</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8985,6 +9380,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945080</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9092,6 +9492,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945082</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9199,6 +9604,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945084</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9306,6 +9716,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945086</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9413,6 +9828,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945087</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9520,6 +9940,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945089</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9627,6 +10052,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945090</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9734,6 +10164,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945091</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9841,6 +10276,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945092</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9948,6 +10388,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945061</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10055,6 +10500,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945063</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10162,6 +10612,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945053</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10264,6 +10719,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123159458</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10366,6 +10826,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123160404</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10468,6 +10933,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123162867</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10570,6 +11040,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123166144</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10682,6 +11157,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945002</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10794,6 +11274,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945004</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10906,6 +11391,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945078</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11008,6 +11498,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123160655</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11110,6 +11605,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123160720</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11222,6 +11722,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945023</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11339,6 +11844,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945047</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11456,6 +11966,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945088</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11568,6 +12083,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945003</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11680,6 +12200,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945007</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11792,6 +12317,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945012</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11904,6 +12434,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945060</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12016,6 +12551,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945033</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12128,6 +12668,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945024</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12240,6 +12785,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945040</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12352,6 +12902,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945041</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12464,6 +13019,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945056</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12576,6 +13136,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945065</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12688,6 +13253,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945071</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12790,6 +13360,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123163160</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12902,6 +13477,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132628770</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13009,8 +13589,131 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945009</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 7619-2025 artfynd.xlsx
+++ b/artfynd/A 7619-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134945038</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>134945050</v>
       </c>
       <c r="B3" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>134945068</v>
       </c>
       <c r="B4" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>134945073</v>
       </c>
       <c r="B5" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>134945077</v>
       </c>
       <c r="B6" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>134945083</v>
       </c>
       <c r="B7" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>134945085</v>
       </c>
       <c r="B8" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>134945010</v>
       </c>
       <c r="B9" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>134945011</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>134945016</v>
       </c>
       <c r="B11" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>134945020</v>
       </c>
       <c r="B12" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>134944975</v>
       </c>
       <c r="B13" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>134945013</v>
       </c>
       <c r="B14" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>134945014</v>
       </c>
       <c r="B15" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>134945015</v>
       </c>
       <c r="B16" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>134945018</v>
       </c>
       <c r="B17" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>134945022</v>
       </c>
       <c r="B18" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>134945030</v>
       </c>
       <c r="B19" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>134945054</v>
       </c>
       <c r="B20" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>134945081</v>
       </c>
       <c r="B21" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>134945031</v>
       </c>
       <c r="B22" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>134945017</v>
       </c>
       <c r="B23" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>134945021</v>
       </c>
       <c r="B24" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>134945032</v>
       </c>
       <c r="B25" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>134945037</v>
       </c>
       <c r="B26" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>134945064</v>
       </c>
       <c r="B27" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>134945072</v>
       </c>
       <c r="B28" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>134945001</v>
       </c>
       <c r="B29" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>134945005</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>134945006</v>
       </c>
       <c r="B51" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>134945008</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>134945019</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>134945026</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>134945027</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>134945028</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>134945029</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>134945034</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>134945035</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>134945036</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>134945043</v>
       </c>
       <c r="B61" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>134945045</v>
       </c>
       <c r="B62" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>134945048</v>
       </c>
       <c r="B63" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>134945049</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>134945051</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>134945052</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>134945055</v>
       </c>
       <c r="B67" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>134945057</v>
       </c>
       <c r="B68" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>134945058</v>
       </c>
       <c r="B69" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>134945059</v>
       </c>
       <c r="B70" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>134945062</v>
       </c>
       <c r="B71" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>134945066</v>
       </c>
       <c r="B72" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>134945067</v>
       </c>
       <c r="B73" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>134945069</v>
       </c>
       <c r="B74" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>134945070</v>
       </c>
       <c r="B75" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>134945074</v>
       </c>
       <c r="B76" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>134945075</v>
       </c>
       <c r="B77" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>134945076</v>
       </c>
       <c r="B78" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>134945079</v>
       </c>
       <c r="B79" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>134945080</v>
       </c>
       <c r="B80" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>134945082</v>
       </c>
       <c r="B81" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>134945084</v>
       </c>
       <c r="B82" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>134945086</v>
       </c>
       <c r="B83" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>134945087</v>
       </c>
       <c r="B84" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>134945089</v>
       </c>
       <c r="B85" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>134945090</v>
       </c>
       <c r="B86" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>134945091</v>
       </c>
       <c r="B87" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>134945092</v>
       </c>
       <c r="B88" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>134945061</v>
       </c>
       <c r="B89" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>134945063</v>
       </c>
       <c r="B90" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>134945053</v>
       </c>
       <c r="B91" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>134945002</v>
       </c>
       <c r="B96" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>134945004</v>
       </c>
       <c r="B97" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>134945078</v>
       </c>
       <c r="B98" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>134945023</v>
       </c>
       <c r="B101" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>134945047</v>
       </c>
       <c r="B102" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>134945088</v>
       </c>
       <c r="B103" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>134945024</v>
       </c>
       <c r="B109" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>134945040</v>
       </c>
       <c r="B110" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>134945041</v>
       </c>
       <c r="B111" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>134945056</v>
       </c>
       <c r="B112" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>134945065</v>
       </c>
       <c r="B113" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>134945071</v>
       </c>
       <c r="B114" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>134945009</v>
       </c>
       <c r="B117" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
